--- a/out/LSTM_Base_repeat_5_000007.xlsx
+++ b/out/LSTM_Base_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.037571854792519</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.037571854792519</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.637571854792519</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.637571854792519</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.637571854792519</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003011362564139999</v>
+        <v>-6.038105188275221e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.471656286716626</v>
+        <v>0.6961042754547568</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.94867912752706</v>
+        <v>1.393284754049746</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.520590323782517</v>
+        <v>0.1043839412694196</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.513544093537053</v>
+        <v>0.9050139873536248</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6509073506056573</v>
+        <v>0.1305139476654237</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.294851098966298</v>
+        <v>1.061674472939382</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9330724375541906</v>
+        <v>0.1870911250288232</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.510456284900738</v>
+        <v>1.305416430128927</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9982030334549974</v>
+        <v>0.2001504448110093</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.037571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.573859157134678</v>
+        <v>1.518640143900103</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.057893280575821</v>
+        <v>0.2121183915624241</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.691519695455984</v>
+        <v>1.742743104207468</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4774075620051145</v>
+        <v>0.09572575083263495</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.587562289793333</v>
+        <v>1.721898468050247</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2305660318000107</v>
+        <v>0.04623051919669491</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.570912393156371</v>
+        <v>1.71855998084306</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1098578497649742</v>
+        <v>0.02202746602705347</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.559878898866955</v>
+        <v>1.716347619634103</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03255011457548362</v>
+        <v>0.006523580880987169</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.515003758731787</v>
+        <v>1.707346355452162</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02153116745877032</v>
+        <v>0.004313887701662389</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.525498256555492</v>
+        <v>1.709447096823808</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01101824918062476</v>
+        <v>0.002204963193759101</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.52598922085344</v>
+        <v>1.709541551479308</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005633314631914838</v>
+        <v>0.001125481580367856</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.526232050799596</v>
+        <v>1.709586259537464</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002115034653029544</v>
+        <v>0.0004203693234568383</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.524823526424111</v>
+        <v>1.70929965271882</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001150008368162043</v>
+        <v>0.0002268266796096673</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.525008153004784</v>
+        <v>1.709332699793215</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005513109653908299</v>
+        <v>0.000106262193078166</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.524960005916485</v>
+        <v>1.709319046125635</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003393842911022641</v>
+        <v>6.387685822045283e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.525087392849022</v>
+        <v>1.70934067507415</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.000175139602559954</v>
+        <v>3.10279205119908e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.525098133141601</v>
+        <v>1.709338859507548</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.292019550909565e-05</v>
+        <v>1.29836763541332e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.525087691140236</v>
+        <v>1.709332746370905</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.128244062155931e-05</v>
+        <v>6.512317399864405e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.525107297121204</v>
+        <v>1.709332779412467</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.064344810800705e-05</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.52509726441891</v>
+        <v>1.70932675070418</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.525089249713696</v>
+        <v>1.709321066170152</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.525085159901208</v>
+        <v>1.709316314894938</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.525079292458523</v>
+        <v>1.709311025747376</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.525074223103154</v>
+        <v>1.709311003013075</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.525069858129186</v>
+        <v>1.709311321293292</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.525070949375642</v>
+        <v>1.709312412539749</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.525070259768507</v>
+        <v>1.709311722932613</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.525070290080908</v>
+        <v>1.709311753245014</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.525070100628398</v>
+        <v>1.709311563792504</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.525070153675102</v>
+        <v>1.709311616839207</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.525070206721804</v>
+        <v>1.70931166988591</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.525070168831302</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.525070040003596</v>
+        <v>1.709311503167702</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.525069896019687</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.52506973687958</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.525069789926283</v>
+        <v>1.709311253090388</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.52506973687958</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.52506973687958</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.525069555005171</v>
+        <v>1.709311018169276</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.52506972172338</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.525069918753989</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.525069759613881</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.525069797504383</v>
+        <v>1.709311260668489</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.525069994534993</v>
+        <v>1.709311457699099</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.525069971800692</v>
+        <v>1.709311434964798</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.525069820238683</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.525069744457682</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.525069842972984</v>
+        <v>1.709311306137091</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.525069850551086</v>
+        <v>1.709311313715192</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.525070115784599</v>
+        <v>1.709311578948705</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.525069820238683</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.525070062737898</v>
+        <v>1.709311525902003</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.525070146097001</v>
+        <v>1.709311609261107</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.525069979378792</v>
+        <v>1.709311442542898</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.525070168831302</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.525069820238683</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.525069615629972</v>
+        <v>1.709311078794079</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.525069729301478</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.525069744457682</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.525069509536568</v>
+        <v>1.709310972700674</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.525069570161371</v>
+        <v>1.709311033325477</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.525069441333665</v>
+        <v>1.70931090449777</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.637571854792519</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.525069577739471</v>
+        <v>1.709311040903577</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.52506975203578</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.525069896019687</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.525069729301478</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.52506972172338</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.525069433755563</v>
+        <v>1.70931089691967</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.525069448911763</v>
+        <v>1.709310912075871</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.525069676254777</v>
+        <v>1.709311139418882</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.525069661098575</v>
+        <v>1.709311124262682</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.525069767191981</v>
+        <v>1.709311230356087</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.525069494380366</v>
+        <v>1.709310957544473</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.525069592895672</v>
+        <v>1.709311056059778</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.525069744457682</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.525069759613881</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.52506973687958</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.525069820238683</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.525069918753989</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.52506975203578</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.52506973687958</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.525069706567178</v>
+        <v>1.709311169731284</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.525069691410977</v>
+        <v>1.709311154575083</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.525069729301478</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.525069744457682</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.52506973687958</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_5_000007.xlsx
+++ b/out/LSTM_Base_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.037571854792519</v>
+        <v>0.8369524225432805</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.037571854792519</v>
+        <v>0.8369524225432804</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003011362564139999</v>
+        <v>-0.0002344359186550137</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.471656286716626</v>
+        <v>2.702699902438257</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.94867912752706</v>
+        <v>5.409577691172822</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.520590323782517</v>
+        <v>0.4052818838180859</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.513544093537053</v>
+        <v>3.513814206769969</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6509073506056573</v>
+        <v>0.5067342249694724</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.294851098966298</v>
+        <v>4.122065202683269</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9330724375541906</v>
+        <v>0.7264011083565102</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.037571854792519</v>
+        <v>0.8369524225432804</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.510456284900738</v>
+        <v>5.068419379165249</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9982030334549974</v>
+        <v>0.7771056486259439</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.573859157134678</v>
+        <v>5.896283401895955</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.057893280575821</v>
+        <v>0.8235746168989275</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.691519695455984</v>
+        <v>6.766387267255702</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4774075620051145</v>
+        <v>0.3716645729904415</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.587562289793333</v>
+        <v>6.685455932383651</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2305660318000107</v>
+        <v>0.1794963580897385</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.570912393156371</v>
+        <v>6.672493927062918</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1098578497649742</v>
+        <v>0.08552467068300207</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.559878898866955</v>
+        <v>6.663904304720973</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03255011457548362</v>
+        <v>0.02534072654215085</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.515003758731787</v>
+        <v>6.628968760092171</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02153116745877032</v>
+        <v>0.01676194563881687</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.525498256555492</v>
+        <v>6.637138693393024</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01101824918062476</v>
+        <v>0.008576072579150986</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.52598922085344</v>
+        <v>6.637519800626333</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005633314631914838</v>
+        <v>0.004385053581464133</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.526232050799596</v>
+        <v>6.637707746038028</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002115034653029544</v>
+        <v>0.00164500911945891</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.524823526424111</v>
+        <v>6.636610142109035</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001150008368162043</v>
+        <v>0.0008942565152118766</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.525008153004784</v>
+        <v>6.636752795048917</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005513109653908299</v>
+        <v>0.000428127823054289</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.524960005916485</v>
+        <v>6.63671419524671</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003393842911022641</v>
+        <v>0.000263619747059766</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.525087392849022</v>
+        <v>6.63681230928113</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.000175139602559954</v>
+        <v>0.0001349942054180214</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.525098133141601</v>
+        <v>6.63681955187008</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.292019550909565e-05</v>
+        <v>6.293833289339209e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.525087691140236</v>
+        <v>6.636810316374807</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.128244062155931e-05</v>
+        <v>3.849097684393219e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.525107297121204</v>
+        <v>6.636824610477088</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.064344810800705e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.52509726441891</v>
+        <v>6.636815607899265</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.525089249713696</v>
+        <v>6.63680814132227</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.525085159901208</v>
+        <v>6.6368038861441</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.525079292458523</v>
+        <v>6.636798163865069</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.525074223103154</v>
+        <v>6.6367930945097</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.525069858129186</v>
+        <v>6.636788729535732</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.525070949375642</v>
+        <v>6.636789820782188</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.525070259768507</v>
+        <v>6.636789131175052</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.525070290080908</v>
+        <v>6.636789161487455</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.525070100628398</v>
+        <v>6.636788972034944</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.525070153675102</v>
+        <v>6.636789025081647</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.525070206721804</v>
+        <v>6.63678907812835</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.525070168831302</v>
+        <v>6.636789040237848</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.525070040003596</v>
+        <v>6.63678891141014</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.525069896019687</v>
+        <v>6.636788767426234</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.52506973687958</v>
+        <v>6.636788608286126</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.525069789926283</v>
+        <v>6.636788661332828</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.52506973687958</v>
+        <v>6.636788608286126</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.52506973687958</v>
+        <v>6.636788608286126</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.525069555005171</v>
+        <v>6.636788426411716</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.52506972172338</v>
+        <v>6.636788593129925</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.525069918753989</v>
+        <v>6.636788790160534</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.525069759613881</v>
+        <v>6.636788631020427</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.525069797504383</v>
+        <v>6.636788668910928</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.525069994534993</v>
+        <v>6.636788865941538</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.525069971800692</v>
+        <v>6.636788843207237</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.525069820238683</v>
+        <v>6.636788691645229</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.525069744457682</v>
+        <v>6.636788615864226</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.525069842972984</v>
+        <v>6.636788714379532</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.525069850551086</v>
+        <v>6.636788721957632</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.525070115784599</v>
+        <v>6.636788987191145</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.525069820238683</v>
+        <v>6.636788691645229</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.525070062737898</v>
+        <v>6.636788934144442</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.525070146097001</v>
+        <v>6.636789017503546</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.525069979378792</v>
+        <v>6.636788850785338</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.525070168831302</v>
+        <v>6.636789040237848</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.525069820238683</v>
+        <v>6.636788691645229</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.525069615629972</v>
+        <v>6.636788487036519</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.525069729301478</v>
+        <v>6.636788600708025</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.525069744457682</v>
+        <v>6.636788615864226</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.525069509536568</v>
+        <v>6.636788380943114</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.525069570161371</v>
+        <v>6.636788441567917</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.525069441333665</v>
+        <v>6.63678831274021</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.525069577739471</v>
+        <v>6.636788449146017</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.52506975203578</v>
+        <v>6.636788623442325</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.525069896019687</v>
+        <v>6.636788767426234</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.525069729301478</v>
+        <v>6.636788600708025</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.52506972172338</v>
+        <v>6.636788593129925</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.525069433755563</v>
+        <v>6.636788305162109</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.525069448911763</v>
+        <v>6.636788320318311</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.525069676254777</v>
+        <v>6.636788547661322</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.525069661098575</v>
+        <v>6.636788532505121</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.525069767191981</v>
+        <v>6.636788638598527</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.525069494380366</v>
+        <v>6.636788365786913</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.525069592895672</v>
+        <v>6.636788464302217</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.525069744457682</v>
+        <v>6.636788615864226</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.525069759613881</v>
+        <v>6.636788631020427</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.52506973687958</v>
+        <v>6.636788608286126</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.525069820238683</v>
+        <v>6.636788691645229</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.525069918753989</v>
+        <v>6.636788790160534</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.52506975203578</v>
+        <v>6.636788623442325</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.52506973687958</v>
+        <v>6.636788608286126</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.525069706567178</v>
+        <v>6.636788577973723</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.525069691410977</v>
+        <v>6.636788562817523</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.525069729301478</v>
+        <v>6.636788600708025</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.525069744457682</v>
+        <v>6.636788615864226</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.52506973687958</v>
+        <v>6.636788608286126</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_5_000007.xlsx
+++ b/out/LSTM_Base_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.02522874996066093</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01227073930203915</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.004456363618373871</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.00429113581776619</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.0007355548441410065</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.036952422543281</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.002049762755632401</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.3109984303716907</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.003514349460601807</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4149555617998992</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.003233488649129868</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.002329427748918533</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001486755907535553</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.001248564571142197</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001216430217027664</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0001913793385028839</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.1109984303716907</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>5.528703331947327e-05</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0003295019268989563</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.036952422543281</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0005644261837005615</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.3109984303716907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0007219277322292328</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4149555617998992</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0009263977408409119</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0003272145986557007</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0004516430199146271</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.036952422543281</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.002101808786392212</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.16</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.004937220364809036</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.762906414714871</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.003634113818407059</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.762906414714871</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.00140775740146637</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.036952422543281</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-4.014745354652405e-05</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0006644986569881439</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.001041948795318604</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0007171817123889923</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.8369524225432805</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001678537577390671</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001115921884775162</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0004720278084278107</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.036952422543281</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0002272985875606537</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.00019097700715065</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1109984303716906</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0002465546131134033</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8369524225432804</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.003109484910964966</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.762906414714871</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0125462394207716</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.762906414714871</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.009459599852561951</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.762906414714871</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.004951372742652893</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.762906414714871</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002344359186550137</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.702699902438257</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.001402288675308228</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.036952422543281</v>
+        <v>0.3</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.409577691172822</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4052818838180859</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.001154579222202301</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.513814206769969</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5067342249694724</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.002991080284118652</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.122065202683269</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7264011083565102</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.001585844904184341</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8369524225432804</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.068419379165249</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.7771056486259439</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.006805840879678726</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.896283401895955</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8235746168989275</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01074386574327946</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.766387267255702</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3716645729904415</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01125064119696617</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>6.685455932383651</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1794963580897385</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.003882754594087601</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>6.672493927062918</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.08552467068300207</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.007937025278806686</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>6.663904304720973</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02534072654215085</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01444865763187408</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>6.628968760092171</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01676194563881687</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01362613216042519</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>6.637138693393024</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.008576072579150986</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01374109089374542</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>6.637519800626333</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004385053581464133</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01046127080917358</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>6.637707746038028</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00164500911945891</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.00813743844628334</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>6.636610142109035</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008942565152118766</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.007132954895496368</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>6.636752795048917</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000428127823054289</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.005879200994968414</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>6.63671419524671</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000263619747059766</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.003630641847848892</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>6.63681230928113</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001349942054180214</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.005302585661411285</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>6.63681955187008</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.293833289339209e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.008946677669882774</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.036952422543281</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>6.636810316374807</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.849097684393219e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.00578739121556282</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.036952422543281</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>6.636824610477088</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.481539171982363e-05</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.00542285293340683</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>6.636815607899265</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>4.264322417369065e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.01043537631630898</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4149555617998992</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>6.63680814132227</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01032743975520134</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>6.6368038861441</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.008966367691755295</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>6.636798163865069</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.004349119961261749</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>6.6367930945097</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.007215052843093872</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>6.636788729535732</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.02094229310750961</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.762906414714871</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>6.636789820782188</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.007603038102388382</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>6.636789131175052</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01100524514913559</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>6.636789161487455</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02061455696821213</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4149555617998992</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>6.636788972034944</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02177383378148079</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>6.636789025081647</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.02133046835660934</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>6.63678907812835</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01843490079045296</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>6.636789040237848</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.0140971951186657</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>6.63678891141014</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01085446774959564</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>6.636788767426234</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.008840035647153854</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>6.636788608286126</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.007091708481311798</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>6.636788661332828</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.00739496573805809</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>6.636788608286126</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.006108388304710388</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>6.636788608286126</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003140099346637726</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>6.636788426411716</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.0007258504629135132</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>6.636788593129925</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002846360206604004</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>6.636788790160534</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005463220179080963</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>6.636788631020427</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003168605268001556</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>6.636788668910928</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0003323443233966827</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>6.636788865941538</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.002979312092065811</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>6.636788843207237</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.006278786808252335</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>6.636788691645229</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.006684400141239166</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>6.636788615864226</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.005345806479454041</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>6.636788714379532</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.001713741570711136</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>6.636788721957632</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.001810260117053986</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>6.636788987191145</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.004013974219560623</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>6.636788691645229</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.002378616482019424</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>6.636788934144442</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.004637047648429871</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>6.636789017503546</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.001010052859783173</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>6.636788850785338</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.002651479095220566</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>6.636789040237848</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.008102424442768097</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4149555617998992</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>6.636788691645229</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01192614063620567</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4149555617998992</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>6.636788487036519</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.011429063975811</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>6.636788600708025</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.008539538830518723</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>6.636788615864226</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.006619255989789963</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>6.636788380943114</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.006554264575242996</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>6.636788441567917</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005911555141210556</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>6.63678831274021</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.0004503019154071808</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>6.636788449146017</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.0004174411296844482</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>6.636788623442325</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.002665411680936813</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4149555617998992</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>6.636788767426234</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003098621964454651</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4149555617998992</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>6.636788600708025</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004135001450777054</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>6.636788593129925</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.006167624145746231</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>6.636788305162109</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.005416776984930038</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>6.636788320318311</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004022795706987381</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>6.636788547661322</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.001397620886564255</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC111" t="n">
-        <v>6.636788532505121</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002671524882316589</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>6.636788638598527</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003652606159448624</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>6.636788365786913</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002551525831222534</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>6.636788464302217</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.001601576805114746</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>6.636788615864226</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.00144483894109726</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>6.636788631020427</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.00117858499288559</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>6.636788608286126</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.0004672445356845856</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>6.636788691645229</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002107448875904083</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>6.636788790160534</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003641799092292786</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>6.636788623442325</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003718260675668716</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>6.636788608286126</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003227356821298599</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>6.636788577973723</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002690237015485764</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>6.636788562817523</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002829518169164658</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>6.636788600708025</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002100888639688492</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.1900000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>6.636788615864226</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0009132549166679382</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6149555617998993</v>
+        <v>1</v>
       </c>
       <c r="JC126" t="n">
-        <v>6.636788608286126</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_5_000007.xlsx
+++ b/out/LSTM_Base_repeat_5_000007.xlsx
@@ -23204,7 +23204,7 @@
         <v>-0.001041948795318604</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0.0007171817123889923</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0.001678537577390671</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0.001115921884775162</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0.0004720278084278107</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
